--- a/EOS_Equipment_Families_and_Categories.xlsx
+++ b/EOS_Equipment_Families_and_Categories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE3A931A-7256-427B-8A98-838521174ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8213E89-D237-4057-8F76-F30CA142AA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="199">
   <si>
     <t>Cooking</t>
   </si>
@@ -557,6 +557,9 @@
   </si>
   <si>
     <t>Laundry Trolley</t>
+  </si>
+  <si>
+    <t>Waste Management</t>
   </si>
   <si>
     <t>Food Waste Disposer</t>
@@ -976,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG31"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
@@ -1012,9 +1015,13 @@
     <col min="31" max="31" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="20.85546875" customWidth="1"/>
     <col min="33" max="33" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1102,16 +1109,25 @@
         <v>168</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AF1" s="1">
         <v>1</v>
       </c>
       <c r="AG1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AI1" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>1</v>
       </c>
@@ -1173,10 +1189,16 @@
         <v>2</v>
       </c>
       <c r="AG2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="AI2">
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>2</v>
       </c>
@@ -1238,10 +1260,16 @@
         <v>3</v>
       </c>
       <c r="AG3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>3</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>3</v>
       </c>
@@ -1303,10 +1331,16 @@
         <v>4</v>
       </c>
       <c r="AG4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+      <c r="AI4">
+        <v>4</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>4</v>
       </c>
@@ -1368,10 +1402,16 @@
         <v>5</v>
       </c>
       <c r="AG5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>5</v>
       </c>
@@ -1433,10 +1473,16 @@
         <v>6</v>
       </c>
       <c r="AG6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="AI6">
+        <v>6</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>6</v>
       </c>
@@ -1498,10 +1544,16 @@
         <v>7</v>
       </c>
       <c r="AG7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>7</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>7</v>
       </c>
@@ -1563,10 +1615,10 @@
         <v>8</v>
       </c>
       <c r="AG8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>8</v>
       </c>
@@ -1623,10 +1675,11 @@
         <v>9</v>
       </c>
       <c r="AG9" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+      <c r="AI9" s="1"/>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>9</v>
       </c>
@@ -1682,10 +1735,10 @@
         <v>10</v>
       </c>
       <c r="AG10" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>10</v>
       </c>
@@ -1742,10 +1795,11 @@
         <v>11</v>
       </c>
       <c r="AG11" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="AI11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>11</v>
       </c>
@@ -1790,10 +1844,10 @@
         <v>12</v>
       </c>
       <c r="AD12" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>12</v>
       </c>
@@ -1819,10 +1873,10 @@
         <v>13</v>
       </c>
       <c r="AD13" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>13</v>
       </c>
@@ -1848,10 +1902,10 @@
         <v>14</v>
       </c>
       <c r="AD14" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>14</v>
       </c>
@@ -1877,10 +1931,10 @@
         <v>15</v>
       </c>
       <c r="AD15" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>15</v>
       </c>
@@ -1906,7 +1960,7 @@
         <v>16</v>
       </c>
       <c r="AD16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="2:30" x14ac:dyDescent="0.25">
@@ -1935,7 +1989,7 @@
         <v>17</v>
       </c>
       <c r="AD17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="2:30" x14ac:dyDescent="0.25">
@@ -1964,7 +2018,7 @@
         <v>18</v>
       </c>
       <c r="AD18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="2:30" x14ac:dyDescent="0.25">
